--- a/0001_ROBOS/CAPTAÇÃO/GSC E SM BAIXA/base_captacao_gerada.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/GSC E SM BAIXA/base_captacao_gerada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -510,23 +510,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yasmim thauany Santos Sousa</t>
+          <t>elizabeth nunes de lima</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>791475620</v>
+        <v>89899267</v>
       </c>
       <c r="G2" t="n">
-        <v>51556288816</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22032007</v>
+        <v>16044997880</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>27297</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11972447489</v>
+        <v>11992334376</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,23 +553,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leticia Machado Gomes da Silva</t>
+          <t>Lorena Nunes Braz Maia</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>94361887</v>
+        <v>93686308</v>
       </c>
       <c r="G3" t="n">
-        <v>17256727747</v>
+        <v>15856041780</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>35972</v>
+        <v>35055</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>21968109838</v>
+        <v>21979447630</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,23 +596,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marlon Ferreira da Silva</t>
+          <t>Bruna Medeiros Aguilera Vernek</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>89657979</v>
+        <v>81808910</v>
       </c>
       <c r="G4" t="n">
-        <v>15200770769</v>
+        <v>15444674785</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>34979</v>
+        <v>34255</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>21978966419</v>
+        <v>21980105075</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -639,23 +639,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bernardo henrique campos</t>
+          <t>Maria Jose do Nascimento Alves</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>95937284</v>
+        <v>82419449</v>
       </c>
       <c r="G5" t="n">
-        <v>52631708822</v>
+        <v>12649400765</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>41278</v>
+        <v>19617</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>11947701709</v>
+        <v>2199148252</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -682,23 +682,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PHILADELFIA OLIVEIRA SILVA</t>
+          <t>laelso dos santos salomao</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>87211361</v>
+        <v>95879928</v>
       </c>
       <c r="G6" t="n">
-        <v>62063809753</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>20158</v>
+        <v>95879928</v>
+      </c>
+      <c r="H6" t="n">
+        <v>95879928</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>21970762968</v>
+        <v>95879928</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -725,23 +725,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maria das Gracas Oliveira Ferreira</t>
+          <t>Fellipe Gil Pereira da Silva</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>93980363</v>
+        <v>95305224</v>
       </c>
       <c r="G7" t="n">
-        <v>94901333704</v>
+        <v>10464831709</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>24854</v>
+        <v>33501</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>21970792925</v>
+        <v>21972355650</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -768,23 +768,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Samuel Lopes</t>
+          <t>angela garcia de souza</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>95472925</v>
+        <v>76610486</v>
       </c>
       <c r="G8" t="n">
-        <v>14356881710</v>
+        <v>10078669855</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>36392</v>
+        <v>25116</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>21968942009</v>
+        <v>11994718055</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,23 +811,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>julia ogando mendonca</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>71827819</v>
+        <v>95609610</v>
       </c>
       <c r="G9" t="n">
-        <v>18356313717</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>36674</v>
+        <v>95609610</v>
+      </c>
+      <c r="H9" t="n">
+        <v>95609610</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>28999411179</v>
+        <v>95609610</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -854,23 +854,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cristiane luci de carvalho silva</t>
+          <t>PLACIDO FERREIRA FERNANDES</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>76479258</v>
+        <v>95309384</v>
       </c>
       <c r="G10" t="n">
-        <v>4793259790</v>
+        <v>9941556709</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>28541</v>
+        <v>30008</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>21998905288</v>
+        <v>21972279953</v>
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -897,23 +897,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ana Beatriz Guerra</t>
+          <t>Suria Iohanna Cerino Cordeiro</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>74749983</v>
+        <v>95686114</v>
       </c>
       <c r="G11" t="n">
-        <v>13508000826</v>
+        <v>16822680713</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>24692</v>
+        <v>41085</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>992584433</v>
+        <v>21990030621</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -940,23 +940,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>iasmine reis dos santos ferreira</t>
+          <t>ana luisa ferreira da silva</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>76479278</v>
+        <v>95570885</v>
       </c>
       <c r="G12" t="n">
-        <v>14707378765</v>
+        <v>15889249711</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>34452</v>
+        <v>37676</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>21993896924</v>
+        <v>21965021427</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -983,23 +983,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rosania maria dantas da silva jeronimo</t>
+          <t>CARLA CRISTINA FERREIRA DO NASCIMENTO</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>93554164</v>
+        <v>96156875</v>
       </c>
       <c r="G13" t="n">
-        <v>1312182717</v>
+        <v>9473197780</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>25460</v>
+        <v>37581</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>21964191280</v>
+        <v>21989546094</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1026,23 +1026,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MARIA LUISA DE CARVALHO CORREA</t>
+          <t>judith lacerda da silva</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>85394345</v>
+        <v>450391639</v>
       </c>
       <c r="G14" t="n">
-        <v>15280561754</v>
+        <v>8595484813</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>38432</v>
+        <v>15786</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>21966887582</v>
+        <v>11982729154</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1069,23 +1069,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>adriana da silva teixeira</t>
+          <t>vanessa batista viana</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>77116110</v>
+        <v>97051509</v>
       </c>
       <c r="G15" t="n">
-        <v>2301906779</v>
+        <v>15788161819</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>26622</v>
+        <v>27719</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>2127517480</v>
+        <v>11975006310</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1112,25 +1112,412 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ARNALDO DOMINGOS DA ROCHA</t>
+          <t>cleiton de lima barroso</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>912661666</v>
+        <v>93232575</v>
       </c>
       <c r="G16" t="n">
-        <v>35114010700</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>19480</v>
+        <v>93232575</v>
+      </c>
+      <c r="H16" t="n">
+        <v>93232575</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>21991053001</v>
+        <v>93232575</v>
       </c>
       <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>iara suzan nascimento silva</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>87919580</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40315840838</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>33572</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>11948411296</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>josemar dos santos martins</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>594344468</v>
+      </c>
+      <c r="G18" t="n">
+        <v>35227173842</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>31770</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>11951748184</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>andrea jesus da paz</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>95147767</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5268124781</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>28807</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>21979863099</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Francisco de assis alves medeiro</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>79235592</v>
+      </c>
+      <c r="G20" t="n">
+        <v>63571110749</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>22413</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>21999921227</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ana carolina de o rebelo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>89209188</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16586682789</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>36743</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>21968358152</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sirlande sa santos</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>97029277</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35624179855</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>31439</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>11916108634</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>bruno alves calazans</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>759046638</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16402827770</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>39204</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>21980963584</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>samara grusman ferraz</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>94995314</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14768024750</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>39578</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>21967514328</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Planilha Total Care</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sthefany Grusman Ferraz</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>94995313</v>
+      </c>
+      <c r="G25" t="n">
+        <v>16653650723</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>38793</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>2174800511</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
